--- a/docs/ValueSet-ahip-reading-language-prereferences.xlsx
+++ b/docs/ValueSet-ahip-reading-language-prereferences.xlsx
@@ -11,13 +11,12 @@
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="157">
   <si>
     <t>Property</t>
   </si>
@@ -52,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -64,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Based on IETF 3066 Language Codes</t>
+    <t>Used as the answer options for the reading language preferences question in the Language Section, capturing the languages and formats a patient prefers when reading health care materials.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -109,31 +108,25 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>amh</t>
+    <t>am</t>
   </si>
   <si>
     <t>Amharic</t>
   </si>
   <si>
-    <t>ara</t>
+    <t>ar</t>
   </si>
   <si>
     <t>Arabic</t>
   </si>
   <si>
-    <t>ath</t>
-  </si>
-  <si>
-    <t>Athabaskan (Na-Deme)</t>
-  </si>
-  <si>
-    <t>ben</t>
+    <t>bn</t>
   </si>
   <si>
     <t>Bengali</t>
   </si>
   <si>
-    <t>bur</t>
+    <t>my</t>
   </si>
   <si>
     <t>Burmese</t>
@@ -142,13 +135,13 @@
     <t>yue</t>
   </si>
   <si>
-    <t>Chinese (Simplified)</t>
-  </si>
-  <si>
-    <t>cha</t>
-  </si>
-  <si>
-    <t>Chamorro</t>
+    <t>Cantonese</t>
+  </si>
+  <si>
+    <t>chr</t>
+  </si>
+  <si>
+    <t>Cherokee</t>
   </si>
   <si>
     <t>chk</t>
@@ -169,61 +162,49 @@
     <t>Dakota</t>
   </si>
   <si>
-    <t>dan</t>
-  </si>
-  <si>
-    <t>Danish</t>
-  </si>
-  <si>
     <t>prs</t>
   </si>
   <si>
     <t>Dari</t>
   </si>
   <si>
-    <t>dut</t>
+    <t>nl</t>
   </si>
   <si>
     <t>Dutch</t>
   </si>
   <si>
-    <t>eng</t>
+    <t>en</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
-    <t>far</t>
+    <t>fa</t>
   </si>
   <si>
     <t>Farsi</t>
   </si>
   <si>
-    <t>fij</t>
-  </si>
-  <si>
-    <t>Fijian</t>
-  </si>
-  <si>
-    <t>fre</t>
+    <t>fr</t>
   </si>
   <si>
     <t>French</t>
   </si>
   <si>
-    <t>ger</t>
+    <t>de</t>
   </si>
   <si>
     <t>German</t>
   </si>
   <si>
-    <t>gre</t>
+    <t>el</t>
   </si>
   <si>
     <t>Greek</t>
   </si>
   <si>
-    <t>hat</t>
+    <t>ht</t>
   </si>
   <si>
     <t>Haitian Creole</t>
@@ -235,13 +216,13 @@
     <t>Hawaiian</t>
   </si>
   <si>
-    <t>heb</t>
+    <t>he</t>
   </si>
   <si>
     <t>Hebrew</t>
   </si>
   <si>
-    <t>hin</t>
+    <t>hi</t>
   </si>
   <si>
     <t>Hindi</t>
@@ -253,25 +234,19 @@
     <t>Hmong</t>
   </si>
   <si>
-    <t>ind</t>
-  </si>
-  <si>
-    <t>Indonesian</t>
-  </si>
-  <si>
-    <t>ipk</t>
+    <t>ik</t>
   </si>
   <si>
     <t>Inupiaq</t>
   </si>
   <si>
-    <t>ita</t>
+    <t>it</t>
   </si>
   <si>
     <t>Italian</t>
   </si>
   <si>
-    <t>jpn</t>
+    <t>ja</t>
   </si>
   <si>
     <t>Japanese</t>
@@ -289,55 +264,37 @@
     <t>Karenni</t>
   </si>
   <si>
-    <t>khm</t>
-  </si>
-  <si>
-    <t>Central Khmer</t>
-  </si>
-  <si>
-    <t>kor</t>
+    <t>km</t>
+  </si>
+  <si>
+    <t>Khmer</t>
+  </si>
+  <si>
+    <t>ko</t>
   </si>
   <si>
     <t>Korean</t>
   </si>
   <si>
-    <t>kos</t>
-  </si>
-  <si>
-    <t>Kosraean</t>
-  </si>
-  <si>
-    <t>kur</t>
-  </si>
-  <si>
-    <t>Kurdish</t>
-  </si>
-  <si>
     <t>lkt</t>
   </si>
   <si>
     <t>Lakota (sioux)</t>
   </si>
   <si>
-    <t>lao</t>
+    <t>lo</t>
   </si>
   <si>
     <t>Lao</t>
   </si>
   <si>
-    <t>lit</t>
-  </si>
-  <si>
-    <t>Lithuanian</t>
-  </si>
-  <si>
     <t>cmn</t>
   </si>
   <si>
-    <t>Chinese (Traditional)</t>
-  </si>
-  <si>
-    <t>mah</t>
+    <t>Mandarin</t>
+  </si>
+  <si>
+    <t>mh</t>
   </si>
   <si>
     <t>Marshallese</t>
@@ -349,25 +306,13 @@
     <t>Muscogee</t>
   </si>
   <si>
-    <t>nav</t>
+    <t>nv</t>
   </si>
   <si>
     <t>Navajo (Dine')</t>
   </si>
   <si>
-    <t>nep</t>
-  </si>
-  <si>
-    <t>Nepali</t>
-  </si>
-  <si>
-    <t>nor</t>
-  </si>
-  <si>
-    <t>Norwegian</t>
-  </si>
-  <si>
-    <t>oji</t>
+    <t>oj</t>
   </si>
   <si>
     <t>Ojibwe</t>
@@ -385,25 +330,13 @@
     <t>Pennsylvania Dutch (Pennsylvania German)</t>
   </si>
   <si>
-    <t>pau</t>
-  </si>
-  <si>
-    <t>Palauan</t>
-  </si>
-  <si>
-    <t>pus</t>
+    <t>ps</t>
   </si>
   <si>
     <t>Pashto</t>
   </si>
   <si>
-    <t>per</t>
-  </si>
-  <si>
-    <t>Persian</t>
-  </si>
-  <si>
-    <t>pol</t>
+    <t>pl</t>
   </si>
   <si>
     <t>Polish</t>
@@ -415,138 +348,90 @@
     <t>Pohnpeian</t>
   </si>
   <si>
-    <t>por</t>
+    <t>pt</t>
   </si>
   <si>
     <t>Portuguese</t>
   </si>
   <si>
-    <t>rus</t>
+    <t>ru</t>
   </si>
   <si>
     <t>Russian</t>
   </si>
   <si>
-    <t>smo</t>
+    <t>sm</t>
   </si>
   <si>
     <t>Samoan</t>
   </si>
   <si>
-    <t>sin</t>
-  </si>
-  <si>
-    <t>Sinhala</t>
-  </si>
-  <si>
-    <t>som</t>
+    <t>so</t>
   </si>
   <si>
     <t>Somali</t>
   </si>
   <si>
-    <t>spa</t>
+    <t>es</t>
   </si>
   <si>
     <t>Spanish</t>
   </si>
   <si>
-    <t>swa</t>
+    <t>sw</t>
   </si>
   <si>
     <t>Swahili</t>
   </si>
   <si>
-    <t>swe</t>
+    <t>sv</t>
   </si>
   <si>
     <t>Swedish</t>
   </si>
   <si>
-    <t>tgl</t>
+    <t>tl</t>
   </si>
   <si>
     <t>Tagalog</t>
   </si>
   <si>
-    <t>tam</t>
-  </si>
-  <si>
-    <t>Tamil</t>
-  </si>
-  <si>
-    <t>tha</t>
+    <t>tnq</t>
+  </si>
+  <si>
+    <t>Taino</t>
+  </si>
+  <si>
+    <t>th</t>
   </si>
   <si>
     <t>Thai</t>
   </si>
   <si>
-    <t>ton</t>
+    <t>to</t>
   </si>
   <si>
     <t>Tongan</t>
   </si>
   <si>
-    <t>tli</t>
-  </si>
-  <si>
-    <t>Tlingit</t>
-  </si>
-  <si>
-    <t>tpi</t>
-  </si>
-  <si>
-    <t>Tok Pisin</t>
-  </si>
-  <si>
-    <t>ukr</t>
-  </si>
-  <si>
-    <t>Ukrainian</t>
-  </si>
-  <si>
-    <t>urd</t>
-  </si>
-  <si>
-    <t>Urdu</t>
-  </si>
-  <si>
-    <t>vie</t>
+    <t>vi</t>
   </si>
   <si>
     <t>Vietnamese</t>
   </si>
   <si>
-    <t>wel</t>
-  </si>
-  <si>
-    <t>Welsh</t>
-  </si>
-  <si>
     <t>apw</t>
   </si>
   <si>
     <t>Western Apache</t>
   </si>
   <si>
-    <t>yap</t>
-  </si>
-  <si>
-    <t>Yapese</t>
-  </si>
-  <si>
-    <t>yid</t>
+    <t>yi</t>
   </si>
   <si>
     <t>Yiddish</t>
   </si>
   <si>
-    <t>ypk</t>
-  </si>
-  <si>
-    <t>Yu'pik</t>
-  </si>
-  <si>
     <t>zun</t>
   </si>
   <si>
@@ -556,37 +441,28 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://tools.ietf.org/html/bcp47</t>
-  </si>
-  <si>
-    <t>tai</t>
-  </si>
-  <si>
-    <t>Taino</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalLanguage</t>
-  </si>
-  <si>
-    <t>x-bra</t>
+    <t>urn:ietf:bcp:47</t>
+  </si>
+  <si>
+    <t>braille</t>
   </si>
   <si>
     <t>Braille</t>
   </si>
   <si>
-    <t>x-lar</t>
+    <t>large-print</t>
   </si>
   <si>
     <t>Large Print</t>
   </si>
   <si>
-    <t>x-dds</t>
+    <t>digital-spoken</t>
   </si>
   <si>
     <t>Digital Documents that Can Be Spoken Out Loud​</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalReadingModes</t>
+    <t>http://terminology.hl7.org/CodeSystem/reading-mode</t>
   </si>
   <si>
     <t>ASKU</t>
@@ -610,7 +486,7 @@
     <t>Please specify if not listed above</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -876,7 +752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1333,170 +1209,18 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>179</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1505,6 +1229,68 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1523,10 +1309,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
@@ -1539,72 +1325,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>189</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1613,52 +1337,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>192</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1677,18 +1355,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>194</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>196</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4">
@@ -1701,10 +1379,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>197</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-reading-language-prereferences.xlsx
+++ b/docs/ValueSet-ahip-reading-language-prereferences.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="155">
   <si>
     <t>Property</t>
   </si>
@@ -478,12 +478,6 @@
   </si>
   <si>
     <t>I choose not to respond at this time</t>
-  </si>
-  <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
@@ -1338,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1363,26 +1357,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-reading-language-prereferences.xlsx
+++ b/docs/ValueSet-ahip-reading-language-prereferences.xlsx
@@ -11,12 +11,13 @@
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
     <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="196">
   <si>
     <t>Property</t>
   </si>
@@ -96,7 +97,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This value set includes codes from IETF BCP 47, Tags for Identifying Languages (RFC 5646 and RFC 4647), published by the Internet Engineering Task Force (IETF). The BCP 47 documents are copyright © IETF Trust and the persons identified as the document authors. For more information see https://www.rfc-editor.org/info/bcp47.
+This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -120,6 +123,12 @@
     <t>Arabic</t>
   </si>
   <si>
+    <t>ath</t>
+  </si>
+  <si>
+    <t>Athabaskan (Na-Dene)</t>
+  </si>
+  <si>
     <t>bn</t>
   </si>
   <si>
@@ -132,10 +141,10 @@
     <t>Burmese</t>
   </si>
   <si>
-    <t>yue</t>
-  </si>
-  <si>
-    <t>Cantonese</t>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>Chamorro</t>
   </si>
   <si>
     <t>chr</t>
@@ -144,6 +153,18 @@
     <t>Cherokee</t>
   </si>
   <si>
+    <t>zh-Hans</t>
+  </si>
+  <si>
+    <t>Chinese (Simplified)</t>
+  </si>
+  <si>
+    <t>zh-Hant</t>
+  </si>
+  <si>
+    <t>Chinese (Traditional)</t>
+  </si>
+  <si>
     <t>chk</t>
   </si>
   <si>
@@ -156,6 +177,12 @@
     <t>Crow</t>
   </si>
   <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>Danish</t>
+  </si>
+  <si>
     <t>dak</t>
   </si>
   <si>
@@ -180,268 +207,367 @@
     <t>English</t>
   </si>
   <si>
+    <t>fj</t>
+  </si>
+  <si>
+    <t>Fijian</t>
+  </si>
+  <si>
+    <t>fr</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>German</t>
+  </si>
+  <si>
+    <t>el</t>
+  </si>
+  <si>
+    <t>Greek</t>
+  </si>
+  <si>
+    <t>ht</t>
+  </si>
+  <si>
+    <t>Haitian Creole</t>
+  </si>
+  <si>
+    <t>haw</t>
+  </si>
+  <si>
+    <t>Hawaiian</t>
+  </si>
+  <si>
+    <t>he</t>
+  </si>
+  <si>
+    <t>Hebrew</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>Hindi</t>
+  </si>
+  <si>
+    <t>hmn</t>
+  </si>
+  <si>
+    <t>Hmong</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
+    <t>ik</t>
+  </si>
+  <si>
+    <t>Inupiaq</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>Italian</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>kar</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>Central Khmer</t>
+  </si>
+  <si>
+    <t>kos</t>
+  </si>
+  <si>
+    <t>Kosraean</t>
+  </si>
+  <si>
+    <t>ko</t>
+  </si>
+  <si>
+    <t>Korean</t>
+  </si>
+  <si>
+    <t>ku</t>
+  </si>
+  <si>
+    <t>Kurdish</t>
+  </si>
+  <si>
+    <t>lkt</t>
+  </si>
+  <si>
+    <t>Lakota (Sioux)</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
+    <t>Lao</t>
+  </si>
+  <si>
+    <t>lt</t>
+  </si>
+  <si>
+    <t>Lithuanian</t>
+  </si>
+  <si>
+    <t>mh</t>
+  </si>
+  <si>
+    <t>Marshallese</t>
+  </si>
+  <si>
+    <t>mus</t>
+  </si>
+  <si>
+    <t>Muscogee</t>
+  </si>
+  <si>
+    <t>nv</t>
+  </si>
+  <si>
+    <t>Navajo (Diné bazaad)</t>
+  </si>
+  <si>
+    <t>ne</t>
+  </si>
+  <si>
+    <t>Nepali</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Norwegian</t>
+  </si>
+  <si>
+    <t>oj</t>
+  </si>
+  <si>
+    <t>Ojibwe</t>
+  </si>
+  <si>
+    <t>ood</t>
+  </si>
+  <si>
+    <t>O'odham</t>
+  </si>
+  <si>
+    <t>pau</t>
+  </si>
+  <si>
+    <t>Palauan</t>
+  </si>
+  <si>
+    <t>ps</t>
+  </si>
+  <si>
+    <t>Pashto</t>
+  </si>
+  <si>
+    <t>pdc</t>
+  </si>
+  <si>
+    <t>Pennsylvania Dutch (Pennsylvania German)</t>
+  </si>
+  <si>
     <t>fa</t>
   </si>
   <si>
-    <t>Farsi</t>
-  </si>
-  <si>
-    <t>fr</t>
-  </si>
-  <si>
-    <t>French</t>
-  </si>
-  <si>
-    <t>de</t>
-  </si>
-  <si>
-    <t>German</t>
-  </si>
-  <si>
-    <t>el</t>
-  </si>
-  <si>
-    <t>Greek</t>
-  </si>
-  <si>
-    <t>ht</t>
-  </si>
-  <si>
-    <t>Haitian Creole</t>
-  </si>
-  <si>
-    <t>haw</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>he</t>
-  </si>
-  <si>
-    <t>Hebrew</t>
-  </si>
-  <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>Hindi</t>
-  </si>
-  <si>
-    <t>hmn</t>
-  </si>
-  <si>
-    <t>Hmong</t>
-  </si>
-  <si>
-    <t>ik</t>
-  </si>
-  <si>
-    <t>Inupiaq</t>
-  </si>
-  <si>
-    <t>it</t>
-  </si>
-  <si>
-    <t>Italian</t>
-  </si>
-  <si>
-    <t>ja</t>
-  </si>
-  <si>
-    <t>Japanese</t>
-  </si>
-  <si>
-    <t>kar</t>
-  </si>
-  <si>
-    <t>Karen</t>
-  </si>
-  <si>
-    <t>kkh</t>
+    <t>Persian (Farsi)</t>
+  </si>
+  <si>
+    <t>pl</t>
+  </si>
+  <si>
+    <t>Polish</t>
+  </si>
+  <si>
+    <t>pon</t>
+  </si>
+  <si>
+    <t>Pohnpeian</t>
+  </si>
+  <si>
+    <t>pt</t>
+  </si>
+  <si>
+    <t>Portuguese</t>
+  </si>
+  <si>
+    <t>ru</t>
+  </si>
+  <si>
+    <t>Russian</t>
+  </si>
+  <si>
+    <t>sm</t>
+  </si>
+  <si>
+    <t>Samoan</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>Sinhala</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>Somali</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>sw</t>
+  </si>
+  <si>
+    <t>Swahili</t>
+  </si>
+  <si>
+    <t>sv</t>
+  </si>
+  <si>
+    <t>Swedish</t>
+  </si>
+  <si>
+    <t>tl</t>
+  </si>
+  <si>
+    <t>Tagalog</t>
+  </si>
+  <si>
+    <t>tnq</t>
+  </si>
+  <si>
+    <t>Taino</t>
+  </si>
+  <si>
+    <t>ta</t>
+  </si>
+  <si>
+    <t>Tamil</t>
+  </si>
+  <si>
+    <t>th</t>
+  </si>
+  <si>
+    <t>Thai</t>
+  </si>
+  <si>
+    <t>tli</t>
+  </si>
+  <si>
+    <t>Tlingit</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>Tongan</t>
+  </si>
+  <si>
+    <t>tpi</t>
+  </si>
+  <si>
+    <t>Tok Pisin</t>
+  </si>
+  <si>
+    <t>uk</t>
+  </si>
+  <si>
+    <t>Ukrainian</t>
+  </si>
+  <si>
+    <t>ur</t>
+  </si>
+  <si>
+    <t>Urdu</t>
+  </si>
+  <si>
+    <t>vi</t>
+  </si>
+  <si>
+    <t>Vietnamese</t>
+  </si>
+  <si>
+    <t>cy</t>
+  </si>
+  <si>
+    <t>Welsh</t>
+  </si>
+  <si>
+    <t>apw</t>
+  </si>
+  <si>
+    <t>Western Apache</t>
+  </si>
+  <si>
+    <t>yap</t>
+  </si>
+  <si>
+    <t>Yapese</t>
+  </si>
+  <si>
+    <t>yi</t>
+  </si>
+  <si>
+    <t>Yiddish</t>
+  </si>
+  <si>
+    <t>ypk</t>
+  </si>
+  <si>
+    <t>Yup'ik</t>
+  </si>
+  <si>
+    <t>zun</t>
+  </si>
+  <si>
+    <t>Zuni</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>urn:ietf:bcp:47</t>
+  </si>
+  <si>
+    <t>KRNI</t>
   </si>
   <si>
     <t>Karenni</t>
   </si>
   <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>Khmer</t>
-  </si>
-  <si>
-    <t>ko</t>
-  </si>
-  <si>
-    <t>Korean</t>
-  </si>
-  <si>
-    <t>lkt</t>
-  </si>
-  <si>
-    <t>Lakota (sioux)</t>
-  </si>
-  <si>
-    <t>lo</t>
-  </si>
-  <si>
-    <t>Lao</t>
-  </si>
-  <si>
-    <t>cmn</t>
-  </si>
-  <si>
-    <t>Mandarin</t>
-  </si>
-  <si>
-    <t>mh</t>
-  </si>
-  <si>
-    <t>Marshallese</t>
-  </si>
-  <si>
-    <t>mus</t>
-  </si>
-  <si>
-    <t>Muscogee</t>
-  </si>
-  <si>
-    <t>nv</t>
-  </si>
-  <si>
-    <t>Navajo (Dine')</t>
-  </si>
-  <si>
-    <t>oj</t>
-  </si>
-  <si>
-    <t>Ojibwe</t>
-  </si>
-  <si>
-    <t>ood</t>
-  </si>
-  <si>
-    <t>O'oodham</t>
-  </si>
-  <si>
-    <t>pdc</t>
-  </si>
-  <si>
-    <t>Pennsylvania Dutch (Pennsylvania German)</t>
-  </si>
-  <si>
-    <t>ps</t>
-  </si>
-  <si>
-    <t>Pashto</t>
-  </si>
-  <si>
-    <t>pl</t>
-  </si>
-  <si>
-    <t>Polish</t>
-  </si>
-  <si>
-    <t>pon</t>
-  </si>
-  <si>
-    <t>Pohnpeian</t>
-  </si>
-  <si>
-    <t>pt</t>
-  </si>
-  <si>
-    <t>Portuguese</t>
-  </si>
-  <si>
-    <t>ru</t>
-  </si>
-  <si>
-    <t>Russian</t>
-  </si>
-  <si>
-    <t>sm</t>
-  </si>
-  <si>
-    <t>Samoan</t>
-  </si>
-  <si>
-    <t>so</t>
-  </si>
-  <si>
-    <t>Somali</t>
-  </si>
-  <si>
-    <t>es</t>
-  </si>
-  <si>
-    <t>Spanish</t>
-  </si>
-  <si>
-    <t>sw</t>
-  </si>
-  <si>
-    <t>Swahili</t>
-  </si>
-  <si>
-    <t>sv</t>
-  </si>
-  <si>
-    <t>Swedish</t>
-  </si>
-  <si>
-    <t>tl</t>
-  </si>
-  <si>
-    <t>Tagalog</t>
-  </si>
-  <si>
-    <t>tnq</t>
-  </si>
-  <si>
-    <t>Taino</t>
-  </si>
-  <si>
-    <t>th</t>
-  </si>
-  <si>
-    <t>Thai</t>
-  </si>
-  <si>
-    <t>to</t>
-  </si>
-  <si>
-    <t>Tongan</t>
-  </si>
-  <si>
-    <t>vi</t>
-  </si>
-  <si>
-    <t>Vietnamese</t>
-  </si>
-  <si>
-    <t>apw</t>
-  </si>
-  <si>
-    <t>Western Apache</t>
-  </si>
-  <si>
-    <t>yi</t>
-  </si>
-  <si>
-    <t>Yiddish</t>
-  </si>
-  <si>
-    <t>zun</t>
-  </si>
-  <si>
-    <t>Zuni</t>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>urn:ietf:bcp:47</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-temporary-codes</t>
   </si>
   <si>
     <t>braille</t>
@@ -459,7 +585,7 @@
     <t>digital-spoken</t>
   </si>
   <si>
-    <t>Digital Documents that Can Be Spoken Out Loud​</t>
+    <t>Digital Documents that Can Be Spoken Out Loud</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/CodeSystem/reading-mode</t>
@@ -480,7 +606,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
@@ -746,7 +872,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1203,18 +1329,170 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1223,6 +1501,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -1241,26 +1565,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>143</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>145</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>147</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
@@ -1273,56 +1597,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>148</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>151</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -1349,10 +1627,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>153</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3">
@@ -1365,10 +1643,56 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>154</v>
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
